--- a/Result/DivideRBM_RQAE_eps0=2^-6_R=12_maxdeg=5_integEpsabs=1e-4.xlsx
+++ b/Result/DivideRBM_RQAE_eps0=2^-6_R=12_maxdeg=5_integEpsabs=1e-4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AE59A1-5A65-43CA-821F-14AC6CA9606C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11590412-6040-4DAD-9B06-9746B513BFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C8CA6423-46CB-412F-AC8C-E0D1306D81BC}"/>
+    <workbookView xWindow="1530" yWindow="1290" windowWidth="17985" windowHeight="8970" xr2:uid="{C8CA6423-46CB-412F-AC8C-E0D1306D81BC}"/>
   </bookViews>
   <sheets>
     <sheet name="DivideRBM_RQAE_eps0=2^-6_R=12_m" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>N</t>
   </si>
@@ -92,6 +92,22 @@
   </si>
   <si>
     <t>totalQueryNum_LowDepthQAE_eps=2^-5_nShot=12</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>RMSE=0.003を達成するのに必要な古典モンテサンプル数</t>
+    <rPh sb="11" eb="13">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コテン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>スウ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -948,33 +964,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'DivideRBM_RQAE_eps0=2^-6_R=12_m'!$P$2:$P$9</c:f>
+              <c:f>'DivideRBM_RQAE_eps0=2^-6_R=12_m'!$Q$2:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>471077.97662358131</c:v>
+                  <c:v>424083.3028489133</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>709625.45827031066</c:v>
+                  <c:v>583114.54141725576</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>757758.52265322336</c:v>
+                  <c:v>848166.6056978266</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1181439.3158887953</c:v>
+                  <c:v>1166229.0828345115</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2290292.6771039208</c:v>
+                  <c:v>1696333.2113956532</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7074241.341472473</c:v>
+                  <c:v>2385468.5785251372</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3181856.7669033953</c:v>
+                  <c:v>3392666.4227913064</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12685567.594383098</c:v>
+                  <c:v>4770937.1570502743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1048,7 +1064,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'DivideRBM_RQAE_eps0=2^-6_R=12_m'!$Q$2:$Q$9</c:f>
+              <c:f>'DivideRBM_RQAE_eps0=2^-6_R=12_m'!$R$2:$R$9</c:f>
               <c:numCache>
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2222,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52491F43-C746-4643-9A5B-486FD276CD47}">
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
@@ -2230,11 +2246,11 @@
     <col min="13" max="13" width="14.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="6.5" customWidth="1"/>
-    <col min="16" max="16" width="51.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="51.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2278,10 +2294,13 @@
         <v>11</v>
       </c>
       <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>8</v>
       </c>
@@ -2327,14 +2346,18 @@
         <v>181</v>
       </c>
       <c r="P2" s="3">
-        <f t="shared" ref="P2" si="3">J2/L2/L2*SQRT($B$2*(1-$B$2))</f>
+        <f>$J2/L2/L2*SQRT($B$2*(1-$B$2))</f>
         <v>471077.97662358131</v>
       </c>
       <c r="Q2" s="3">
+        <f>$J2/0.003^2*SQRT($B$2*(1-$B$2))</f>
+        <v>424083.3028489133</v>
+      </c>
+      <c r="R2" s="3">
         <v>53136</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>11</v>
       </c>
@@ -2351,7 +2374,7 @@
         <v>3.5261706738816101E-3</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F66" si="4">E3*E3</f>
+        <f t="shared" ref="F3:F66" si="3">E3*E3</f>
         <v>1.2433879621342689E-5</v>
       </c>
       <c r="G3">
@@ -2368,7 +2391,7 @@
         <v>2.2468019029159699E-3</v>
       </c>
       <c r="L3" s="2">
-        <f t="shared" ref="L3:L8" si="5">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
+        <f t="shared" ref="L3:L8" si="4">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
         <v>2.7194657703146848E-3</v>
       </c>
       <c r="M3" s="3">
@@ -2384,10 +2407,14 @@
         <v>709625.45827031066</v>
       </c>
       <c r="Q3" s="3">
+        <f t="shared" ref="Q3:Q10" si="5">$J3/0.003^2*SQRT($B$2*(1-$B$2))</f>
+        <v>583114.54141725576</v>
+      </c>
+      <c r="R3" s="3">
         <v>109296</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>16</v>
       </c>
@@ -2404,7 +2431,7 @@
         <v>2.6807000131870901E-3</v>
       </c>
       <c r="F4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7.1861525607012651E-6</v>
       </c>
       <c r="G4">
@@ -2421,7 +2448,7 @@
         <v>2.93042720863232E-3</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.1739232780715739E-3</v>
       </c>
       <c r="M4" s="3">
@@ -2437,10 +2464,14 @@
         <v>757758.52265322336</v>
       </c>
       <c r="Q4" s="3">
+        <f t="shared" si="5"/>
+        <v>848166.6056978266</v>
+      </c>
+      <c r="R4" s="3">
         <v>254592</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>22</v>
       </c>
@@ -2457,7 +2488,7 @@
         <v>3.8762056773818899E-3</v>
       </c>
       <c r="F5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.5024970453367596E-5</v>
       </c>
       <c r="G5">
@@ -2474,7 +2505,7 @@
         <v>2.5918364063663062E-3</v>
       </c>
       <c r="L5" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.9806259544054416E-3</v>
       </c>
       <c r="M5" s="3">
@@ -2490,10 +2521,14 @@
         <v>1181439.3158887953</v>
       </c>
       <c r="Q5" s="3">
+        <f t="shared" si="5"/>
+        <v>1166229.0828345115</v>
+      </c>
+      <c r="R5" s="3">
         <v>582912</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>32</v>
       </c>
@@ -2510,7 +2545,7 @@
         <v>2.4869306362492699E-3</v>
       </c>
       <c r="F6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.1848239895151986E-6</v>
       </c>
       <c r="G6">
@@ -2527,7 +2562,7 @@
         <v>2.1713035189890274E-3</v>
       </c>
       <c r="L6" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.5818520085813365E-3</v>
       </c>
       <c r="M6" s="3">
@@ -2543,10 +2578,14 @@
         <v>2290292.6771039208</v>
       </c>
       <c r="Q6" s="3">
+        <f t="shared" si="5"/>
+        <v>1696333.2113956532</v>
+      </c>
+      <c r="R6" s="3">
         <v>1596672</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>45</v>
       </c>
@@ -2563,7 +2602,7 @@
         <v>1.36181812499813E-3</v>
       </c>
       <c r="F7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8545486055734225E-6</v>
       </c>
       <c r="G7">
@@ -2580,7 +2619,7 @@
         <v>1.4357685768576517E-3</v>
       </c>
       <c r="L7" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.742080297258297E-3</v>
       </c>
       <c r="M7" s="3">
@@ -2596,10 +2635,14 @@
         <v>7074241.341472473</v>
       </c>
       <c r="Q7" s="3">
+        <f t="shared" si="5"/>
+        <v>2385468.5785251372</v>
+      </c>
+      <c r="R7" s="3">
         <v>3949560</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>64</v>
       </c>
@@ -2616,7 +2659,7 @@
         <v>4.8575538121955397E-3</v>
       </c>
       <c r="F8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.3595829038375422E-5</v>
       </c>
       <c r="G8">
@@ -2633,7 +2676,7 @@
         <v>2.7024430215764994E-3</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>3.097786780677896E-3</v>
       </c>
       <c r="M8" s="3">
@@ -2649,10 +2692,14 @@
         <v>3181856.7669033953</v>
       </c>
       <c r="Q8" s="3">
+        <f t="shared" si="5"/>
+        <v>3392666.4227913064</v>
+      </c>
+      <c r="R8" s="3">
         <v>9584640</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>90</v>
       </c>
@@ -2669,7 +2716,7 @@
         <v>4.4461251806604502E-4</v>
       </c>
       <c r="F9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.976802912210292E-7</v>
       </c>
       <c r="G9">
@@ -2702,10 +2749,14 @@
         <v>12685567.594383098</v>
       </c>
       <c r="Q9" s="3">
+        <f t="shared" si="5"/>
+        <v>4770937.1570502743</v>
+      </c>
+      <c r="R9" s="3">
         <v>24324300</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2722,7 +2773,7 @@
         <v>4.8673061624759901E-4</v>
       </c>
       <c r="F10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.369066927927675E-7</v>
       </c>
       <c r="G10">
@@ -2755,10 +2806,14 @@
         <v>3733076.7170903417</v>
       </c>
       <c r="Q10" s="3">
+        <f t="shared" si="5"/>
+        <v>6785332.8455826128</v>
+      </c>
+      <c r="R10" s="3">
         <v>58452480</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>11</v>
       </c>
@@ -2775,7 +2830,7 @@
         <v>9.4466252306657495E-4</v>
       </c>
       <c r="F11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>8.923872824865073E-7</v>
       </c>
       <c r="G11">
@@ -2785,7 +2840,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>16</v>
       </c>
@@ -2802,7 +2857,7 @@
         <v>2.2494068838742002E-3</v>
       </c>
       <c r="F12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.0598313292206392E-6</v>
       </c>
       <c r="G12">
@@ -2812,7 +2867,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>22</v>
       </c>
@@ -2829,7 +2884,7 @@
         <v>5.0575738141956901E-3</v>
       </c>
       <c r="F13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.5579052886037943E-5</v>
       </c>
       <c r="G13">
@@ -2839,7 +2894,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>32</v>
       </c>
@@ -2856,7 +2911,7 @@
         <v>8.5715377219142098E-4</v>
       </c>
       <c r="F14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7.3471258918198245E-7</v>
       </c>
       <c r="G14">
@@ -2866,7 +2921,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>45</v>
       </c>
@@ -2883,7 +2938,7 @@
         <v>3.8120631495007699E-3</v>
       </c>
       <c r="F15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.4531825455781729E-5</v>
       </c>
       <c r="G15">
@@ -2893,7 +2948,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>64</v>
       </c>
@@ -2910,7 +2965,7 @@
         <v>2.4573137881931302E-3</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.0383910536440721E-6</v>
       </c>
       <c r="G16">
@@ -2937,7 +2992,7 @@
         <v>3.3682687700627898E-3</v>
       </c>
       <c r="F17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1345234507380298E-5</v>
       </c>
       <c r="G17">
@@ -2964,7 +3019,7 @@
         <v>3.4921686487232497E-4</v>
       </c>
       <c r="F18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.2195241871125567E-7</v>
       </c>
       <c r="G18">
@@ -2991,7 +3046,7 @@
         <v>1.1509331501293699E-3</v>
       </c>
       <c r="F19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.3246471160667147E-6</v>
       </c>
       <c r="G19">
@@ -3018,7 +3073,7 @@
         <v>3.16824876806254E-3</v>
       </c>
       <c r="F20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.0037800256329802E-5</v>
       </c>
       <c r="G20">
@@ -3045,7 +3100,7 @@
         <v>3.0511231691311399E-3</v>
       </c>
       <c r="F21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.30935259320885E-6</v>
       </c>
       <c r="G21">
@@ -3072,7 +3127,7 @@
         <v>3.1494968928750199E-3</v>
       </c>
       <c r="F22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.9193306782294051E-6</v>
       </c>
       <c r="G22">
@@ -3099,7 +3154,7 @@
         <v>4.3672561574725701E-4</v>
       </c>
       <c r="F23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9072926344982078E-7</v>
       </c>
       <c r="G23">
@@ -3126,7 +3181,7 @@
         <v>4.21210315350106E-3</v>
       </c>
       <c r="F24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.7741812975733576E-5</v>
       </c>
       <c r="G24">
@@ -3153,7 +3208,7 @@
         <v>4.3211126794118199E-4</v>
       </c>
       <c r="F25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8672014788173596E-7</v>
       </c>
       <c r="G25">
@@ -3180,7 +3235,7 @@
         <v>4.8836689350351104E-4</v>
       </c>
       <c r="F26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.385022226702697E-7</v>
       </c>
       <c r="G26">
@@ -3207,7 +3262,7 @@
         <v>1.25830639878032E-4</v>
       </c>
       <c r="F27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.5833349932114977E-8</v>
       </c>
       <c r="G27">
@@ -3234,7 +3289,7 @@
         <v>3.0573737941937901E-3</v>
       </c>
       <c r="F28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.3475345174229316E-6</v>
       </c>
       <c r="G28">
@@ -3261,7 +3316,7 @@
         <v>1.5072187786920801E-3</v>
       </c>
       <c r="F29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.2717084468420453E-6</v>
       </c>
       <c r="G29">
@@ -3288,7 +3343,7 @@
         <v>2.5119331364994398E-3</v>
       </c>
       <c r="F30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.3098080822439137E-6</v>
       </c>
       <c r="G30">
@@ -3315,7 +3370,7 @@
         <v>3.9460751756581399E-4</v>
       </c>
       <c r="F31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.5571509291945419E-7</v>
       </c>
       <c r="G31">
@@ -3342,7 +3397,7 @@
         <v>1.51808375156092E-3</v>
       </c>
       <c r="F32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.3045782767532769E-6</v>
       </c>
       <c r="G32">
@@ -3369,7 +3424,7 @@
         <v>1.49933187637352E-3</v>
       </c>
       <c r="F33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.2479960755097404E-6</v>
       </c>
       <c r="G33">
@@ -3396,7 +3451,7 @@
         <v>1.38331890003118E-4</v>
       </c>
       <c r="F34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9135711791834736E-8</v>
       </c>
       <c r="G34">
@@ -3423,7 +3478,7 @@
         <v>2.3369156347491302E-3</v>
       </c>
       <c r="F35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.4611746839349296E-6</v>
       </c>
       <c r="G35">
@@ -3450,7 +3505,7 @@
         <v>4.2808600291887001E-3</v>
       </c>
       <c r="F36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8325762589505478E-5</v>
       </c>
       <c r="G36">
@@ -3477,7 +3532,7 @@
         <v>4.9186861871830503E-5</v>
       </c>
       <c r="F37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.4193473807985331E-9</v>
       </c>
       <c r="G37">
@@ -3504,7 +3559,7 @@
         <v>1.54308625181098E-3</v>
       </c>
       <c r="F38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.3811151805280594E-6</v>
       </c>
       <c r="G38">
@@ -3531,7 +3586,7 @@
         <v>1.7759956563799799E-3</v>
       </c>
       <c r="F39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.1541605714805557E-6</v>
       </c>
       <c r="G39">
@@ -3558,7 +3613,7 @@
         <v>2.0618881319990302E-3</v>
       </c>
       <c r="F40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.2513826688784501E-6</v>
       </c>
       <c r="G40">
@@ -3585,7 +3640,7 @@
         <v>7.7425936912278704E-4</v>
       </c>
       <c r="F41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.994775706744162E-7</v>
       </c>
       <c r="G41">
@@ -3612,7 +3667,7 @@
         <v>3.6808000231880402E-3</v>
       </c>
       <c r="F42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.3548288810701078E-5</v>
       </c>
       <c r="G42">
@@ -3639,7 +3694,7 @@
         <v>4.3825063074450698E-3</v>
       </c>
       <c r="F43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.920636153479582E-5</v>
       </c>
       <c r="G43">
@@ -3666,7 +3721,7 @@
         <v>3.2557575189375802E-3</v>
       </c>
       <c r="F44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.0599957022118587E-5</v>
       </c>
       <c r="G44">
@@ -3693,7 +3748,7 @@
         <v>4.6183937825639001E-3</v>
       </c>
       <c r="F45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1329561130824889E-5</v>
       </c>
       <c r="G45">
@@ -3720,7 +3775,7 @@
         <v>5.1309450376896201E-3</v>
       </c>
       <c r="F46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.6326596979791737E-5</v>
       </c>
       <c r="G46">
@@ -3747,7 +3802,7 @@
         <v>4.8673061624715497E-4</v>
       </c>
       <c r="F47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.3690669279233525E-7</v>
       </c>
       <c r="G47">
@@ -3774,7 +3829,7 @@
         <v>5.56848879206495E-3</v>
       </c>
       <c r="F48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.1008067427352966E-5</v>
       </c>
       <c r="G48">
@@ -3801,7 +3856,7 @@
         <v>2.0260206588800199E-3</v>
       </c>
       <c r="F49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.10475971020863E-6</v>
       </c>
       <c r="G49">
@@ -3828,7 +3883,7 @@
         <v>3.95121317813196E-3</v>
       </c>
       <c r="F50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.5612085579043664E-5</v>
       </c>
       <c r="G50">
@@ -3855,7 +3910,7 @@
         <v>7.6015782146355796E-3</v>
       </c>
       <c r="F51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.7783991353222249E-5</v>
       </c>
       <c r="G51">
@@ -3882,7 +3937,7 @@
         <v>3.0136194187561E-3</v>
       </c>
       <c r="F52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.0819020011038541E-6</v>
       </c>
       <c r="G52">
@@ -3909,7 +3964,7 @@
         <v>4.3058625294386497E-3</v>
       </c>
       <c r="F53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8540452122423808E-5</v>
       </c>
       <c r="G53">
@@ -3936,7 +3991,7 @@
         <v>2.35105316213035E-3</v>
       </c>
       <c r="F54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.5274509711631175E-6</v>
       </c>
       <c r="G54">
@@ -3963,7 +4018,7 @@
         <v>1.1321812749416299E-3</v>
       </c>
       <c r="F55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.2818344393284546E-6</v>
       </c>
       <c r="G55">
@@ -3990,7 +4045,7 @@
         <v>1.15554749793556E-3</v>
       </c>
       <c r="F56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.335290019985133E-6</v>
       </c>
       <c r="G56">
@@ -4017,7 +4072,7 @@
         <v>1.4134594027545E-3</v>
       </c>
       <c r="F57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9978674832351078E-6</v>
       </c>
       <c r="G57">
@@ -4044,7 +4099,7 @@
         <v>2.0993918823738402E-3</v>
       </c>
       <c r="F58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.4074462757771762E-6</v>
       </c>
       <c r="G58">
@@ -4071,7 +4126,7 @@
         <v>2.6932012633120702E-3</v>
       </c>
       <c r="F59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7.2533330447057306E-6</v>
       </c>
       <c r="G59">
@@ -4098,7 +4153,7 @@
         <v>2.1931512583116498E-3</v>
       </c>
       <c r="F60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.8099124418339726E-6</v>
       </c>
       <c r="G60">
@@ -4125,7 +4180,7 @@
         <v>4.7762956863828202E-3</v>
       </c>
       <c r="F61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.2813000483759137E-5</v>
       </c>
       <c r="G61">
@@ -4152,7 +4207,7 @@
         <v>2.69595016315848E-4</v>
       </c>
       <c r="F62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7.2681472822342353E-8</v>
       </c>
       <c r="G62">
@@ -4179,7 +4234,7 @@
         <v>1.6430962528109999E-3</v>
       </c>
       <c r="F63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.6997652960015495E-6</v>
       </c>
       <c r="G63">
@@ -4206,7 +4261,7 @@
         <v>4.1335939275344199E-4</v>
       </c>
       <c r="F64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.708659875774943E-7</v>
       </c>
       <c r="G64">
@@ -4233,7 +4288,7 @@
         <v>9.6341439825398101E-4</v>
       </c>
       <c r="F65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.2816730276308037E-7</v>
       </c>
       <c r="G65">
@@ -4260,7 +4315,7 @@
         <v>1.5618381269984999E-3</v>
       </c>
       <c r="F66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.4393383349461824E-6</v>
       </c>
       <c r="G66">
